--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136969419</v>
       </c>
       <c r="B2" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136969420</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136969419</v>
       </c>
       <c r="B2" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136969420</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136969419</v>
       </c>
       <c r="B2" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136969420</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136969419</v>
       </c>
       <c r="B2" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136969420</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136969419</v>
       </c>
       <c r="B2" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>136969420</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136969419</v>
+        <v>137227729</v>
       </c>
       <c r="B2" t="n">
-        <v>79520</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Korpimäki, Dlr</t>
+          <t>Blåkullmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481142</v>
+        <v>481113</v>
       </c>
       <c r="R2" t="n">
-        <v>6815252</v>
+        <v>6815122</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,68 +761,53 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136969419</t>
+          <t>https://artportalen.se/Sighting/137227729</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136969420</v>
+        <v>136969419</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481150</v>
+        <v>481142</v>
       </c>
       <c r="R3" t="n">
-        <v>6815244</v>
+        <v>6815252</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,59 +903,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136969420</t>
+          <t>https://artportalen.se/Sighting/136969419</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136968595</v>
+        <v>137225812</v>
       </c>
       <c r="B4" t="n">
-        <v>58008</v>
+        <v>92357</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>3008</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>N Korpimäki, Dlr</t>
+          <t>Blåkullmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481097</v>
+        <v>481113</v>
       </c>
       <c r="R4" t="n">
-        <v>6815246</v>
+        <v>6815122</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,27 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flera träd</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,49 +994,49 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Tobias Hellberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136968595</t>
+          <t>https://artportalen.se/Sighting/137225812</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136968599</v>
+        <v>136969420</v>
       </c>
       <c r="B5" t="n">
-        <v>58164</v>
+        <v>79501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103023</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1091,13 +1046,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>481170</v>
+        <v>481150</v>
       </c>
       <c r="R5" t="n">
-        <v>6815171</v>
+        <v>6815244</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,20 +1102,1227 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Bengt Oldhammer, Birgitta Kvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136969420</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136968595</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>N Korpimäki, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>481097</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6815246</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera träd</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136968595</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137225840</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Blåkullmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>481123</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6815131</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137225840</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137225856</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Blåkullmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>481131</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6815115</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137225856</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137225869</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Blåkullmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>481125</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6815184</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137225869</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137225896</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Blåkullmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>481109</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6815226</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137225896</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137225931</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Blåkullmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>481117</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6815207</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137225931</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137225949</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Blåkullmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>481138</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6815184</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137225949</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137225955</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Blåkullmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>481163</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6815167</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137225955</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137228068</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Blåkullmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>481158</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6815083</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137228068</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137229738</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57199</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Blåkullmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>481154</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6815060</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Uppflog Gråal förekommer i området, en förutsättning för järprevir</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tobias Hellberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137229738</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136968599</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58177</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>N Korpimäki, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>481170</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6815171</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136968599</t>
         </is>
@@ -1172,6 +2334,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227729</v>
       </c>
       <c r="B2" t="n">
-        <v>92370</v>
+        <v>92372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136969419</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137225812</v>
       </c>
       <c r="B4" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136969420</v>
       </c>
       <c r="B5" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136968595</v>
       </c>
       <c r="B6" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>137225840</v>
       </c>
       <c r="B7" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>137225856</v>
       </c>
       <c r="B8" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>137225869</v>
       </c>
       <c r="B9" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>137225896</v>
       </c>
       <c r="B10" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137225931</v>
       </c>
       <c r="B11" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>137225949</v>
       </c>
       <c r="B12" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>137225955</v>
       </c>
       <c r="B13" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>137228068</v>
       </c>
       <c r="B14" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         <v>137229738</v>
       </c>
       <c r="B15" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136968599</v>
       </c>
       <c r="B16" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -1167,11 +1167,7 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>N Korpimäki, Dlr</t>
@@ -1289,11 +1285,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Blåkullmyren, Dlr</t>
@@ -1396,11 +1388,7 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Blåkullmyren, Dlr</t>
@@ -1503,11 +1491,7 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Blåkullmyren, Dlr</t>
@@ -1610,11 +1594,7 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Blåkullmyren, Dlr</t>
@@ -1717,11 +1697,7 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Blåkullmyren, Dlr</t>
@@ -1824,11 +1800,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Blåkullmyren, Dlr</t>
@@ -2033,11 +2005,7 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Blåkullmyren, Dlr</t>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227729</v>
       </c>
       <c r="B2" t="n">
-        <v>92372</v>
+        <v>92375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137225812</v>
       </c>
       <c r="B4" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227729</v>
       </c>
       <c r="B2" t="n">
-        <v>92375</v>
+        <v>92385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136969419</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137225812</v>
       </c>
       <c r="B4" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136969420</v>
       </c>
       <c r="B5" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136968595</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137225840</v>
       </c>
       <c r="B7" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>137225856</v>
       </c>
       <c r="B8" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>137225869</v>
       </c>
       <c r="B9" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>137225896</v>
       </c>
       <c r="B10" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>137225931</v>
       </c>
       <c r="B11" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>137225949</v>
       </c>
       <c r="B12" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>137225955</v>
       </c>
       <c r="B13" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137228068</v>
       </c>
       <c r="B14" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>137229738</v>
       </c>
       <c r="B15" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>136968599</v>
       </c>
       <c r="B16" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227729</v>
       </c>
       <c r="B2" t="n">
-        <v>92385</v>
+        <v>92386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137225812</v>
       </c>
       <c r="B4" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227729</v>
       </c>
       <c r="B2" t="n">
-        <v>92386</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136969419</v>
       </c>
       <c r="B3" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137225812</v>
       </c>
       <c r="B4" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136969420</v>
       </c>
       <c r="B5" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136968595</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137225840</v>
       </c>
       <c r="B7" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>137225856</v>
       </c>
       <c r="B8" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>137225869</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>137225896</v>
       </c>
       <c r="B10" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>137225931</v>
       </c>
       <c r="B11" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>137225949</v>
       </c>
       <c r="B12" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>137225955</v>
       </c>
       <c r="B13" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137228068</v>
       </c>
       <c r="B14" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>137229738</v>
       </c>
       <c r="B15" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>136968599</v>
       </c>
       <c r="B16" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227729</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137225812</v>
       </c>
       <c r="B4" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227729</v>
       </c>
       <c r="B2" t="n">
-        <v>92391</v>
+        <v>92396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136969419</v>
       </c>
       <c r="B3" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137225812</v>
       </c>
       <c r="B4" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136969420</v>
       </c>
       <c r="B5" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136968595</v>
       </c>
       <c r="B6" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137225840</v>
       </c>
       <c r="B7" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>137225856</v>
       </c>
       <c r="B8" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>137225869</v>
       </c>
       <c r="B9" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>137225896</v>
       </c>
       <c r="B10" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>137225931</v>
       </c>
       <c r="B11" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>137225949</v>
       </c>
       <c r="B12" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>137225955</v>
       </c>
       <c r="B13" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137228068</v>
       </c>
       <c r="B14" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>136968599</v>
       </c>
       <c r="B16" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227729</v>
       </c>
       <c r="B2" t="n">
-        <v>92396</v>
+        <v>92408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136969419</v>
       </c>
       <c r="B3" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137225812</v>
       </c>
       <c r="B4" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136969420</v>
       </c>
       <c r="B5" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227729</v>
       </c>
       <c r="B2" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136969419</v>
       </c>
       <c r="B3" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137225812</v>
       </c>
       <c r="B4" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136969420</v>
       </c>
       <c r="B5" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227729</v>
       </c>
       <c r="B2" t="n">
-        <v>92409</v>
+        <v>92412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136969419</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137225812</v>
       </c>
       <c r="B4" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136969420</v>
       </c>
       <c r="B5" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136969419</v>
       </c>
       <c r="B3" t="n">
-        <v>79567</v>
+        <v>79568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136969420</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37647-2023 artfynd.xlsx
+++ b/artfynd/A 37647-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137227729</v>
       </c>
       <c r="B2" t="n">
-        <v>92412</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136969419</v>
       </c>
       <c r="B3" t="n">
-        <v>79568</v>
+        <v>79571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>137225812</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136969420</v>
       </c>
       <c r="B5" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>136968595</v>
       </c>
       <c r="B6" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>137225840</v>
       </c>
       <c r="B7" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>137225856</v>
       </c>
       <c r="B8" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>137225869</v>
       </c>
       <c r="B9" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>137225896</v>
       </c>
       <c r="B10" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>137225931</v>
       </c>
       <c r="B11" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>137225949</v>
       </c>
       <c r="B12" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>137225955</v>
       </c>
       <c r="B13" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>137228068</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>137229738</v>
       </c>
       <c r="B15" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>136968599</v>
       </c>
       <c r="B16" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
